--- a/data/trans_orig/IP42E-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP42E-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40055</t>
+          <t>40577</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50159</t>
+          <t>50083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47602</t>
+          <t>48212</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58115</t>
+          <t>58494</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>91313</t>
+          <t>92117</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105763</t>
+          <t>105486</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,53%</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3212</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4927</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>693</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9015</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>762</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3411</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1240</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7521</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11397</t>
+          <t>10992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4123</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>12834</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>8841</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20784</t>
+          <t>20137</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>250702</t>
+          <t>251192</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>276818</t>
+          <t>277321</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>283528</t>
+          <t>283220</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>309336</t>
+          <t>308668</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>543316</t>
+          <t>543561</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>579802</t>
+          <t>579619</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,32%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7638</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19063</t>
+          <t>19033</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>10559</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22921</t>
+          <t>23096</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21047</t>
+          <t>20885</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37313</t>
+          <t>38183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>5765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1852</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7943</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1985,7 +1985,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4436</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>860</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7914</t>
+          <t>7400</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1502</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11002</t>
+          <t>11284</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>24329</t>
+          <t>23736</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8559</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21058</t>
+          <t>21183</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22797</t>
+          <t>23248</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40075</t>
+          <t>40070</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12922</t>
+          <t>13100</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2741</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>10722</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,12 +2276,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>20450</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2319,12 +2319,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31184</t>
+          <t>32218</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>51310</t>
+          <t>50593</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2334,12 +2334,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,12 +2354,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38155</t>
+          <t>38092</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58251</t>
+          <t>57760</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,12 +2389,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75748</t>
+          <t>75443</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>103770</t>
+          <t>102657</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>99215</t>
+          <t>99816</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>116925</t>
+          <t>117262</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89265</t>
+          <t>88468</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>106947</t>
+          <t>106154</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>194894</t>
+          <t>194725</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>220269</t>
+          <t>219636</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,19%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4574</t>
+          <t>4524</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13459</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15245</t>
+          <t>15072</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>11617</t>
+          <t>12210</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>25108</t>
+          <t>25665</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6513</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5103</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7343</t>
+          <t>7970</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9829</t>
+          <t>8758</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3001,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8775</t>
+          <t>8841</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>19595</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>13475</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15611</t>
+          <t>15660</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29930</t>
+          <t>30128</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -3114,12 +3114,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>7191</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3129,12 +3129,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8341</t>
+          <t>8187</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13069</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -3227,12 +3227,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19281</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7722</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18442</t>
+          <t>18670</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3277,12 +3277,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17359</t>
+          <t>17460</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>32568</t>
+          <t>32904</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3312,12 +3312,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>403201</t>
+          <t>403273</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>434977</t>
+          <t>434901</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>430633</t>
+          <t>432587</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>463716</t>
+          <t>466291</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>843521</t>
+          <t>844000</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>888914</t>
+          <t>889716</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,99%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14689</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>28878</t>
+          <t>28134</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>18786</t>
+          <t>18474</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34371</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>37143</t>
+          <t>35685</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>58731</t>
+          <t>56820</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4684</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>15227</t>
+          <t>14246</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -3796,12 +3796,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>645</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5723</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3682</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12227</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15522</t>
+          <t>15303</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3881,12 +3881,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3909,12 +3909,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>23889</t>
+          <t>23007</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>41257</t>
+          <t>41278</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3944,12 +3944,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>17145</t>
+          <t>18389</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>33949</t>
+          <t>34329</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3959,12 +3959,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,12 +3979,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>45562</t>
+          <t>46654</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>69529</t>
+          <t>70344</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -4022,12 +4022,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>8647</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>19864</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4037,82 +4037,82 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>10784</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>6450</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>17172</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>2,92%</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>24311</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>17322</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>33660</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>3,59%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>10784</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>6630</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>17699</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="O33" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="P33" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R33" s="2" t="inlineStr">
-        <is>
-          <t>24311</t>
-        </is>
-      </c>
-      <c r="S33" s="2" t="inlineStr">
-        <is>
-          <t>17628</t>
-        </is>
-      </c>
-      <c r="T33" s="2" t="inlineStr">
-        <is>
-          <t>33225</t>
-        </is>
-      </c>
-      <c r="U33" s="2" t="inlineStr">
-        <is>
-          <t>2,13%</t>
-        </is>
-      </c>
-      <c r="V33" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -4135,12 +4135,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>47489</t>
+          <t>47640</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>72184</t>
+          <t>71422</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4150,12 +4150,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>55938</t>
+          <t>54676</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>80261</t>
+          <t>80227</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4185,12 +4185,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>109554</t>
+          <t>111321</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>145346</t>
+          <t>145206</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48096</t>
+          <t>48323</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59703</t>
+          <t>59998</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47435</t>
+          <t>48157</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57039</t>
+          <t>57357</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>99288</t>
+          <t>99440</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114496</t>
+          <t>114477</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,37%</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4341</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4784,7 +4784,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5751</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4877,7 +4877,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4912,7 +4912,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1191</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6597</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5236,7 +5236,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6648</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17236</t>
+          <t>17065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12685</t>
+          <t>12362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>12181</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25728</t>
+          <t>25985</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>263042</t>
+          <t>262350</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>288679</t>
+          <t>288699</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>289500</t>
+          <t>289505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>317956</t>
+          <t>317285</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>557799</t>
+          <t>562579</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>599186</t>
+          <t>599307</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,97%</t>
         </is>
       </c>
     </row>
@@ -5617,12 +5617,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>9123</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21417</t>
+          <t>22628</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5652,12 +5652,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>13302</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26376</t>
+          <t>26871</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5667,12 +5667,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5687,12 +5687,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>25835</t>
+          <t>25505</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44956</t>
+          <t>43143</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5702,12 +5702,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -5735,7 +5735,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6663</t>
+          <t>6383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5750,7 +5750,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5765,12 +5765,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>568</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5100</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5800,12 +5800,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5815,12 +5815,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -5848,7 +5848,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5878,12 +5878,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>8158</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8746</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21755</t>
+          <t>21379</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5991,12 +5991,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13726</t>
+          <t>13389</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>28570</t>
+          <t>28680</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6026,12 +6026,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25474</t>
+          <t>25487</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43838</t>
+          <t>45170</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -6069,12 +6069,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2888</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6104,12 +6104,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8710</t>
+          <t>8282</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6139,12 +6139,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6313</t>
+          <t>6544</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16972</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6154,12 +6154,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -6182,12 +6182,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33561</t>
+          <t>33912</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53584</t>
+          <t>54077</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37879</t>
+          <t>37847</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>59037</t>
+          <t>59179</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6232,12 +6232,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6252,12 +6252,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76405</t>
+          <t>76232</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>106172</t>
+          <t>106570</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6267,12 +6267,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,04%</t>
         </is>
       </c>
     </row>
@@ -6412,12 +6412,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>100613</t>
+          <t>100481</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>117724</t>
+          <t>118647</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6427,12 +6427,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>94599</t>
+          <t>93316</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112913</t>
+          <t>112974</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6462,12 +6462,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6482,12 +6482,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>200652</t>
+          <t>199401</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>228148</t>
+          <t>225481</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6497,12 +6497,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>74,59%</t>
         </is>
       </c>
     </row>
@@ -6525,12 +6525,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>7053</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>18721</t>
+          <t>19040</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6560,12 +6560,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17100</t>
+          <t>16449</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6575,12 +6575,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6595,12 +6595,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>15472</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32829</t>
+          <t>30344</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6610,12 +6610,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8323</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6653,12 +6653,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>794</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6928</t>
+          <t>6214</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6708,12 +6708,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2645</t>
+          <t>2672</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11578</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,0%</t>
         </is>
       </c>
     </row>
@@ -6756,7 +6756,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6786,12 +6786,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>776</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6495</t>
+          <t>6522</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6801,12 +6801,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6821,12 +6821,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -6864,12 +6864,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1994</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7762</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19427</t>
+          <t>19513</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6914,12 +6914,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6934,12 +6934,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>11854</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25599</t>
+          <t>25467</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6949,12 +6949,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -6977,12 +6977,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6992,12 +6992,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8184</t>
+          <t>8023</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>14232</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -7090,12 +7090,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9491</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22190</t>
+          <t>22431</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7105,12 +7105,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>10262</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23074</t>
+          <t>23418</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>22372</t>
+          <t>23013</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39849</t>
+          <t>39718</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -7320,12 +7320,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>425042</t>
+          <t>424532</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>459450</t>
+          <t>458409</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>441398</t>
+          <t>443122</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>477129</t>
+          <t>478962</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>875951</t>
+          <t>876259</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>925852</t>
+          <t>925533</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7405,12 +7405,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,46%</t>
+          <t>77,43%</t>
         </is>
       </c>
     </row>
@@ -7433,12 +7433,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>19852</t>
+          <t>19506</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>36956</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>22225</t>
+          <t>22645</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>40156</t>
+          <t>39849</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7483,12 +7483,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46905</t>
+          <t>45937</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>73182</t>
+          <t>70215</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7518,12 +7518,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -7546,12 +7546,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11735</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2423</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>10296</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7055</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>18393</t>
+          <t>18932</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2652</t>
+          <t>2985</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10654</t>
+          <t>10872</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3753</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>13801</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -7772,12 +7772,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>15599</t>
+          <t>15291</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30552</t>
+          <t>30550</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>24538</t>
+          <t>23691</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>43096</t>
+          <t>42429</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43868</t>
+          <t>43522</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>68306</t>
+          <t>67027</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -7885,12 +7885,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>18005</t>
+          <t>17786</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>5333</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>15921</t>
+          <t>15510</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>13995</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>29432</t>
+          <t>28444</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -7998,12 +7998,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>57906</t>
+          <t>56052</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>83092</t>
+          <t>82234</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8013,12 +8013,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8033,12 +8033,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>59339</t>
+          <t>58109</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>84966</t>
+          <t>84994</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -8068,12 +8068,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>123732</t>
+          <t>121760</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>161800</t>
+          <t>157282</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -8459,12 +8459,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36973</t>
+          <t>36684</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42603</t>
+          <t>42313</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8474,12 +8474,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8494,12 +8494,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35508</t>
+          <t>34808</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39739</t>
+          <t>39723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8509,12 +8509,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8529,12 +8529,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>74220</t>
+          <t>74240</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81549</t>
+          <t>81735</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8544,12 +8544,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -8612,7 +8612,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>3435</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8627,7 +8627,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8647,7 +8647,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>3331</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>3,98%</t>
         </is>
       </c>
     </row>
@@ -9064,7 +9064,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3302</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>3637</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6573</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9152,12 +9152,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9207,12 +9207,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1128</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6954</t>
+          <t>7432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -9367,12 +9367,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>265131</t>
+          <t>264895</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>286730</t>
+          <t>286904</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9382,12 +9382,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9402,12 +9402,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>281538</t>
+          <t>282222</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>303412</t>
+          <t>303807</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9417,12 +9417,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>556748</t>
+          <t>555727</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>587840</t>
+          <t>585760</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -9480,12 +9480,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3277</t>
+          <t>2862</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>12218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9515,12 +9515,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>11257</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9530,12 +9530,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9550,12 +9550,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7199</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>19420</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -9598,7 +9598,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9613,7 +9613,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9668,7 +9668,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -9711,7 +9711,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3138</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9761,7 +9761,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -9819,12 +9819,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>13899</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9854,12 +9854,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15610</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9889,12 +9889,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11159</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25379</t>
+          <t>24579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,62%</t>
         </is>
       </c>
     </row>
@@ -9932,12 +9932,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8330</t>
+          <t>8275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9947,12 +9947,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9972,7 +9972,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10002,12 +10002,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9671</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -10045,12 +10045,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28950</t>
+          <t>29837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48519</t>
+          <t>48326</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24235</t>
+          <t>24378</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43037</t>
+          <t>42484</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -10115,12 +10115,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>58527</t>
+          <t>58474</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83983</t>
+          <t>84638</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -10275,12 +10275,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>113847</t>
+          <t>113191</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>128314</t>
+          <t>127821</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10290,12 +10290,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10310,12 +10310,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>110726</t>
+          <t>110126</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>127569</t>
+          <t>128054</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10325,12 +10325,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>70,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>227289</t>
+          <t>229374</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>251566</t>
+          <t>251226</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,14%</t>
         </is>
       </c>
     </row>
@@ -10388,12 +10388,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12887</t>
+          <t>12609</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18142</t>
+          <t>17811</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10458,12 +10458,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>13482</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27095</t>
+          <t>27771</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -10506,7 +10506,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4855</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10521,7 +10521,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6616</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10571,12 +10571,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1414</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>8593</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>3176</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -10732,7 +10732,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4735</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10762,12 +10762,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10777,12 +10777,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10797,12 +10797,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12130</t>
+          <t>12105</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10915,7 +10915,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4788</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -10953,12 +10953,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>7311</t>
+          <t>7059</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17797</t>
+          <t>17765</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10968,12 +10968,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10988,12 +10988,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23351</t>
+          <t>23293</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11023,12 +11023,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20181</t>
+          <t>19879</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>36764</t>
+          <t>36110</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>424946</t>
+          <t>424933</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>451894</t>
+          <t>453920</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -11218,12 +11218,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>436857</t>
+          <t>436492</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>465309</t>
+          <t>465351</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11233,7 +11233,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -11253,12 +11253,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>871915</t>
+          <t>870386</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>909984</t>
+          <t>909948</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -11296,12 +11296,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>8863</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>21070</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -11311,12 +11311,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -11331,12 +11331,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12462</t>
+          <t>12639</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>27134</t>
+          <t>27208</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -11366,12 +11366,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>22969</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>41628</t>
+          <t>40826</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -11409,12 +11409,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6240</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -11429,7 +11429,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11449,7 +11449,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7188</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2065</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9853</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5506</t>
+          <t>5438</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11557,12 +11557,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>523</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11592,12 +11592,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8369</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -11635,12 +11635,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>4859</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>15472</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11650,12 +11650,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11670,12 +11670,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>9120</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21887</t>
+          <t>22213</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11705,12 +11705,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>17034</t>
+          <t>17072</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>33214</t>
+          <t>33527</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11725,7 +11725,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -11748,12 +11748,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9245</t>
+          <t>8616</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -11783,12 +11783,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -11803,7 +11803,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -11818,12 +11818,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>12393</t>
+          <t>11482</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -11861,12 +11861,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>42998</t>
+          <t>41853</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>65381</t>
+          <t>64442</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>38598</t>
+          <t>38509</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>59829</t>
+          <t>60345</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -11931,12 +11931,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>86954</t>
+          <t>85453</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>118900</t>
+          <t>117847</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -11946,12 +11946,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,08%</t>
         </is>
       </c>
     </row>
@@ -12392,7 +12392,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>354</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1867</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -13265,7 +13265,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1092</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
@@ -13315,7 +13315,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -13687,7 +13687,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2161</t>
+          <t>2041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13772,7 +13772,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -13948,7 +13948,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2926</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13963,7 +13963,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13983,7 +13983,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3539</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13998,7 +13998,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>41,04%</t>
         </is>
       </c>
     </row>
@@ -15046,7 +15046,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -15096,7 +15096,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>11266</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -15131,12 +15131,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>95,51%</t>
         </is>
       </c>
     </row>
@@ -15503,7 +15503,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -15573,7 +15573,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -15588,7 +15588,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -15779,7 +15779,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -15814,7 +15814,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
